--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3DB401-A55B-4160-9D51-A4E97FE42C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6B2140-88AC-444B-99E4-42730B4E74E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1183,21 +1183,25 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="13">
+        <v>46229</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1020</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6B2140-88AC-444B-99E4-42730B4E74E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF692491-E2DF-4D8A-83F8-B9C1190FD081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>NOT BAD</t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
 </sst>
 </file>
@@ -1183,25 +1186,21 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>46229</v>
-      </c>
-      <c r="B10" s="14">
-        <v>420</v>
-      </c>
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
-      <c r="I10" s="15">
+      <c r="I10" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>420</v>
-      </c>
-      <c r="J10" s="15">
+        <v/>
+      </c>
+      <c r="J10" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v/>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
@@ -1297,25 +1296,47 @@
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>370</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>420</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Desktop\PRIYANKAGIT\CAP-776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF692491-E2DF-4D8A-83F8-B9C1190FD081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41EA7C3-8B9C-4F87-B3D2-6DA4CCB0B97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,60 @@
   </si>
   <si>
     <t>medium</t>
+  </si>
+  <si>
+    <t>exciting</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>very excited and exploring new things about cooding .</t>
+  </si>
+  <si>
+    <t>very nice</t>
+  </si>
+  <si>
+    <t>I was missing my brother on account of rakhi</t>
+  </si>
+  <si>
+    <t>nice</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>due to fever</t>
+  </si>
+  <si>
+    <t>due to high fever ,cold and cough</t>
+  </si>
+  <si>
+    <t>nice weathjer = good mood</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>due to fever am not done well in my english  C.A .</t>
+  </si>
+  <si>
+    <t>good day</t>
+  </si>
+  <si>
+    <t>not bad</t>
+  </si>
+  <si>
+    <t>satifying day</t>
+  </si>
+  <si>
+    <t>excellent</t>
+  </si>
+  <si>
+    <t>very high</t>
+  </si>
+  <si>
+    <t>fantastic ca of dbms</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1366,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
@@ -1322,11 +1376,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>970</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
@@ -1339,291 +1393,553 @@
       </c>
       <c r="N15" s="17"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>280</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>300</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>220</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="D18" s="14">
+        <v>300</v>
+      </c>
+      <c r="E18" s="14">
+        <v>220</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>860</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="D19" s="14">
+        <v>260</v>
+      </c>
+      <c r="E19" s="14">
+        <v>200</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>860</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46265</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>200</v>
+      </c>
+      <c r="F20" s="14">
+        <v>100</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="D21" s="14">
+        <v>350</v>
+      </c>
+      <c r="E21" s="14">
+        <v>350</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>45</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+        <v>345</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>200</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="D23" s="14">
+        <v>200</v>
+      </c>
+      <c r="E23" s="14">
+        <v>180</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>45</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>815</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>180</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>770</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+      <c r="A25" s="13">
+        <v>46270</v>
+      </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>280</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>740</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
+      <c r="A26" s="13">
+        <v>46271</v>
+      </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="D26" s="14">
+        <v>300</v>
+      </c>
+      <c r="E26" s="14">
+        <v>220</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>180</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>740</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13">
+        <v>46272</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="D27" s="14">
+        <v>200</v>
+      </c>
+      <c r="E27" s="14">
+        <v>200</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13">
+        <v>46273</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="D28" s="14">
+        <v>180</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>730</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
